--- a/static/standards-correlations/Louisiana_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Louisiana_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$53</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Louisiana CS Standards, BESE-approved October 2024</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Louisiana CS Standards, BESE-approved October 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -847,7 +848,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) traces a file from the student's machine across the internet to a remote server and back. Discovery Systems 9 supplies the sender-receiver-protocol model.</t>
+          <t>Ext 5.3F (Talking to a Server) traces a file from the student's machine across the internet to a remote server and back. Introductory Systems 9 supplies the sender-receiver-protocol model.</t>
         </is>
       </c>
     </row>
@@ -972,7 +973,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and why emotional pressure works; Ext 5.3G (Secret Messages / HTTPS) covers credential interception. Malware is not covered.</t>
+          <t>Introductory Systems 10 covers phishing and why emotional pressure works; Ext 5.3G (Secret Messages / HTTPS) covers credential interception. Malware is not covered.</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2010,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Students ship a working minimum run then iterate, which is the MVP shape, and Discovery Systems 5 teaches the design cycle. The SDLC is never named or staged formally.</t>
+          <t>Students ship a working minimum run then iterate, which is the MVP shape, and Introductory Systems 5 teaches the design cycle. The SDLC is never named or staged formally.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2100,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Louisiana names all three. Students work in a real IDE from PreLab 1, Unit 5.3 teaches repositories, commits, and push and pull, and Discovery Systems 13 assigns rotating team roles.</t>
+          <t>Louisiana names all three. Students work in a real IDE from PreLab 1, Unit 5.3 teaches repositories, commits, and push and pull, and Introductory Systems 13 assigns rotating team roles.</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 12 covers how computing changed the world at an elementary level. Milestones and the people behind them are not studied.</t>
+          <t>Introductory Systems 12 covers how computing changed the world at an elementary level. Milestones and the people behind them are not studied.</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2413,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3H (Find the Community) covers repository norms such as stars and issues, and Discovery Systems 11 covers online conduct. The physical-to-cyber adaptation framing is absent.</t>
+          <t>Ext 5.3H (Find the Community) covers repository norms such as stars and issues, and Introductory Systems 11 covers online conduct. The physical-to-cyber adaptation framing is absent.</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2585,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and why emotional pressure works, which is motive analysis at an elementary level.</t>
+          <t>Introductory Systems 10 covers phishing and why emotional pressure works, which is motive analysis at an elementary level.</t>
         </is>
       </c>
     </row>
@@ -2849,6 +2850,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2893,7 +2895,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2907,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2993,6 +2995,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
@@ -3010,7 +3014,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed directly from the official LDOE standards document, not a third-party framework.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
